--- a/model_templates/ark.ClinicalMetadataTemplate.xlsx
+++ b/model_templates/ark.ClinicalMetadataTemplate.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -134,7 +134,7 @@
     </comment>
     <comment authorId="0" ref="X1">
       <text>
-        <t xml:space="preserve">A high-level classification of vitiligo based on the distribution and patterning of lesions across the body.</t>
+        <t xml:space="preserve">TBD</t>
       </text>
     </comment>
     <comment authorId="0" ref="C2">
@@ -15127,7 +15127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="85">
   <si>
     <t>Component</t>
   </si>
@@ -15240,9 +15240,6 @@
     <t>gestational</t>
   </si>
   <si>
-    <t>mixed</t>
-  </si>
-  <si>
     <t>AMP RA/SLE</t>
   </si>
   <si>
@@ -15276,9 +15273,6 @@
     <t>type 1</t>
   </si>
   <si>
-    <t>non-segmental</t>
-  </si>
-  <si>
     <t>Community Contribution</t>
   </si>
   <si>
@@ -15309,9 +15303,6 @@
     <t>type 2</t>
   </si>
   <si>
-    <t>segmental</t>
-  </si>
-  <si>
     <t>RA</t>
   </si>
   <si>
@@ -15330,13 +15321,10 @@
     <t>Hashimoto's Thyroiditis</t>
   </si>
   <si>
-    <t>unclassified</t>
-  </si>
-  <si>
     <t>SLE</t>
   </si>
   <si>
-    <t>lupus nephritis</t>
+    <t>discoid lupus erythematosus</t>
   </si>
   <si>
     <t>Mixed Race</t>
@@ -15348,7 +15336,7 @@
     <t>STAMP</t>
   </si>
   <si>
-    <t>OA</t>
+    <t>lupus nephritis</t>
   </si>
   <si>
     <t>Native Hawaiian or Other Pacific Islander</t>
@@ -15357,34 +15345,40 @@
     <t>multiple sclerosis</t>
   </si>
   <si>
-    <t>V-CoRT</t>
+    <t>UMass V-CoRT</t>
+  </si>
+  <si>
+    <t>Not Applicable</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>OA</t>
   </si>
   <si>
     <t>psoriasis</t>
   </si>
   <si>
-    <t>other</t>
+    <t>White</t>
   </si>
   <si>
     <t>psoriatic arthritis</t>
   </si>
   <si>
-    <t>White</t>
+    <t>pulmonary disease</t>
+  </si>
+  <si>
+    <t>rheumatoid arthritis</t>
   </si>
   <si>
     <t>scleroderma</t>
   </si>
   <si>
-    <t>pulmonary disease</t>
+    <t>systemic lupus erythematosus</t>
   </si>
   <si>
     <t>Sjogren's disease</t>
-  </si>
-  <si>
-    <t>rheumatoid arthritis</t>
-  </si>
-  <si>
-    <t>systemic lupus erythematosus</t>
   </si>
   <si>
     <t>vitiligo</t>
@@ -15510,6 +15504,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42788,22 +42786,22 @@
       <c r="Y1000" s="6"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="R1:R1000">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$P1 = "psoriasis"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="V1:V1000">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
       <formula>$P1 = "diabetes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R1000">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
-      <formula>$P1 = "psoriasis"</formula>
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$F1 = "psoriasis"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:X1000">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$F1 = "vitiligo"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T1:T1000">
     <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
@@ -42813,19 +42811,19 @@
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:S1000">
+  <conditionalFormatting sqref="T1:T1000">
     <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1:Q1000">
+  <conditionalFormatting sqref="S1:S1000">
     <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>$F1 = "dermatomyositis"</formula>
+      <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R1000">
+  <conditionalFormatting sqref="Q1:Q1000">
     <cfRule type="expression" dxfId="0" priority="8" stopIfTrue="1">
-      <formula>$F1 = "psoriasis"</formula>
+      <formula>$F1 = "dermatomyositis"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W1000">
@@ -42853,9 +42851,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="K2:K1000">
       <formula1>Sheet2!$K$2:$K$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="X2:X1000">
-      <formula1>Sheet2!$X$2:$X$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
       <formula1>Sheet2!$H$2:$H$3</formula1>
@@ -42993,208 +42988,206 @@
       <c r="V2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="X2" s="7" t="s">
+    </row>
+    <row r="3">
+      <c r="B3" s="7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="V3" s="7" t="s">
+    </row>
+    <row r="4">
+      <c r="B4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="C4" s="7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="J4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="K4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="P4" s="7" t="s">
+    </row>
+    <row r="5">
+      <c r="C5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="I5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="C5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="O5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" s="7" t="s">
+      <c r="P5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="V5" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="O5" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="V5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="X5" s="7" t="s">
+      <c r="P6" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="7" t="s">
+    <row r="7">
+      <c r="C7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P7" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7">
-      <c r="C7" s="7" t="s">
+    <row r="8">
+      <c r="C8" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P8" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="F9" s="7" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="7" t="s">
+      <c r="J9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F8" s="7" t="s">
+    </row>
+    <row r="10">
+      <c r="F10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="P10" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="P8" s="7" t="s">
+    </row>
+    <row r="11">
+      <c r="F11" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="F9" s="7" t="s">
+      <c r="P11" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>55</v>
+    </row>
+    <row r="12">
+      <c r="F12" s="7" t="s">
+        <v>58</v>
       </c>
-      <c r="P9" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="F10" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" s="7" t="s">
+      <c r="P12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="P10" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11" s="7" t="s">
+    </row>
+    <row r="13">
+      <c r="F13" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P13" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="12">
-      <c r="F12" s="7" t="s">
+    <row r="14">
+      <c r="F14" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="P12" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="F13" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="F14" s="7" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>86</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/model_templates/ark.ClinicalMetadataTemplate.xlsx
+++ b/model_templates/ark.ClinicalMetadataTemplate.xlsx
@@ -134,7 +134,7 @@
     </comment>
     <comment authorId="0" ref="X1">
       <text>
-        <t xml:space="preserve">TBD</t>
+        <t xml:space="preserve">A high-level classification of vitiligo based on the distribution and patterning of lesions across the body.</t>
       </text>
     </comment>
     <comment authorId="0" ref="C2">
@@ -15127,7 +15127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="89">
   <si>
     <t>Component</t>
   </si>
@@ -15198,7 +15198,7 @@
     <t>visitID</t>
   </si>
   <si>
-    <t>vitiligoType</t>
+    <t>vitiligoPattern</t>
   </si>
   <si>
     <t>ClinicalMetadataTemplate</t>
@@ -15240,6 +15240,9 @@
     <t>gestational</t>
   </si>
   <si>
+    <t>mixed</t>
+  </si>
+  <si>
     <t>AMP RA/SLE</t>
   </si>
   <si>
@@ -15273,6 +15276,9 @@
     <t>type 1</t>
   </si>
   <si>
+    <t>non-segmental</t>
+  </si>
+  <si>
     <t>Community Contribution</t>
   </si>
   <si>
@@ -15303,6 +15309,9 @@
     <t>type 2</t>
   </si>
   <si>
+    <t>segmental</t>
+  </si>
+  <si>
     <t>RA</t>
   </si>
   <si>
@@ -15319,6 +15328,9 @@
   </si>
   <si>
     <t>Hashimoto's Thyroiditis</t>
+  </si>
+  <si>
+    <t>unclassified</t>
   </si>
   <si>
     <t>SLE</t>
@@ -15732,7 +15744,7 @@
     <col customWidth="1" min="21" max="21" width="3.88"/>
     <col customWidth="1" min="22" max="22" width="8.75"/>
     <col customWidth="1" min="23" max="23" width="4.63"/>
-    <col customWidth="1" min="24" max="24" width="7.75"/>
+    <col customWidth="1" min="24" max="24" width="9.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -42786,19 +42798,19 @@
       <c r="Y1000" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="R1:R1000">
+  <conditionalFormatting sqref="V1:V1000">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$P1 = "psoriasis"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V1:V1000">
-    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
       <formula>$P1 = "diabetes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R1000">
+    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
+      <formula>$P1 = "psoriasis"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S1:S1000">
     <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$F1 = "psoriasis"</formula>
+      <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:X1000">
@@ -42806,19 +42818,19 @@
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U1:U1000">
+  <conditionalFormatting sqref="T1:T1000">
     <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:T1000">
+  <conditionalFormatting sqref="U1:U1000">
     <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:S1000">
+  <conditionalFormatting sqref="R1:R1000">
     <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
-      <formula>$F1 = "vitiligo"</formula>
+      <formula>$F1 = "psoriasis"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q1:Q1000">
@@ -42828,12 +42840,12 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W1000">
     <cfRule type="expression" dxfId="1" priority="9" stopIfTrue="1">
-      <formula>$B1 = "AMP RA/SLE"</formula>
+      <formula>$B1 = "AMP AIM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W1000">
     <cfRule type="expression" dxfId="1" priority="10" stopIfTrue="1">
-      <formula>$B1 = "AMP AIM"</formula>
+      <formula>$B1 = "AMP RA/SLE"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
@@ -42851,6 +42863,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="K2:K1000">
       <formula1>Sheet2!$K$2:$K$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="X2:X1000">
+      <formula1>Sheet2!$X$2:$X$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="H2:H1000">
       <formula1>Sheet2!$H$2:$H$3</formula1>
@@ -42988,206 +43003,218 @@
       <c r="V2" s="7" t="s">
         <v>36</v>
       </c>
+      <c r="X2" s="7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="X3" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="V4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="C5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="J5" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="F9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="F10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="F11" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="F12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>62</v>
+      <c r="P12" s="7" t="s">
+        <v>84</v>
       </c>
-      <c r="P5" s="7" t="s">
-        <v>63</v>
+    </row>
+    <row r="13">
+      <c r="F13" s="7" t="s">
+        <v>85</v>
       </c>
-      <c r="V5" s="7" t="s">
-        <v>53</v>
+      <c r="P13" s="7" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="6">
-      <c r="C6" s="7" t="s">
-        <v>64</v>
+    <row r="14">
+      <c r="F14" s="7" t="s">
+        <v>87</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="C7" s="7" t="s">
+    </row>
+    <row r="15">
+      <c r="F15" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="F9" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="F10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="F12" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="F13" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="F14" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="F15" s="7" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="F17" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/model_templates/ark.ClinicalMetadataTemplate.xlsx
+++ b/model_templates/ark.ClinicalMetadataTemplate.xlsx
@@ -42808,7 +42808,7 @@
       <formula>$P1 = "psoriasis"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1:S1000">
+  <conditionalFormatting sqref="U1:U1000">
     <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
@@ -42823,7 +42823,7 @@
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U1:U1000">
+  <conditionalFormatting sqref="S1:S1000">
     <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>$F1 = "vitiligo"</formula>
     </cfRule>
@@ -42840,12 +42840,12 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W1000">
     <cfRule type="expression" dxfId="1" priority="9" stopIfTrue="1">
-      <formula>$B1 = "AMP AIM"</formula>
+      <formula>$B1 = "AMP RA/SLE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W1000">
     <cfRule type="expression" dxfId="1" priority="10" stopIfTrue="1">
-      <formula>$B1 = "AMP RA/SLE"</formula>
+      <formula>$B1 = "AMP AIM"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
